--- a/src/main/resources/assets/template/ImportBinEntryTemplate.xlsx
+++ b/src/main/resources/assets/template/ImportBinEntryTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backend\kvc-wh-be\src\main\resources\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0FA110-95FD-441B-9811-AE78A5A06142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C16DD6-4AEF-4226-9BB4-E576B07D7431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1710" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,10 +36,10 @@
     <t>RECEIVING DATE</t>
   </si>
   <si>
-    <t>ISSUE DATE</t>
+    <t>STATUS</t>
   </si>
   <si>
-    <t>STATUS</t>
+    <t>INSP DATE</t>
   </si>
 </sst>
 </file>
@@ -410,10 +410,10 @@
         <v>0</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/assets/template/ImportBinEntryTemplate.xlsx
+++ b/src/main/resources/assets/template/ImportBinEntryTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backend\kvc-wh-be\src\main\resources\assets\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backend\kvc-wh-be\target\classes\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C16DD6-4AEF-4226-9BB4-E576B07D7431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B780475-AA2F-49F2-9996-7788791B6199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1710" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>BIN</t>
   </si>
@@ -40,15 +40,15 @@
   </si>
   <si>
     <t>INSP DATE</t>
+  </si>
+  <si>
+    <t>QTY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy/mm/dd;@"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -99,14 +99,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -389,30 +385,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22" style="2" customWidth="1"/>
-    <col min="4" max="4" width="29.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
